--- a/docs/tutorials/files/xslope_reinforced_slope.xlsx
+++ b/docs/tutorials/files/xslope_reinforced_slope.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C0E255-0472-174F-97B1-AC3DD61E05E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D385E8-F13F-8F45-A02D-F28142715816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="314">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -1116,6 +1116,12 @@
   </si>
   <si>
     <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
 </sst>
 </file>
@@ -1886,16 +1892,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1910,8 +1916,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2035,6 +2041,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2081,6 +2112,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2788,7 +2823,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3188,18 +3223,18 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>194</v>
       </c>
@@ -3237,34 +3272,40 @@
         <v>252</v>
       </c>
       <c r="M2" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="R2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="S2" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="T2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3291,11 +3332,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3">
@@ -3307,35 +3348,37 @@
       <c r="L3" s="3">
         <v>4.0</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3">
         <v>0.0</v>
       </c>
-      <c r="N3" s="3">
+      <c r="P3" s="3">
         <v>0.0</v>
       </c>
-      <c r="O3" s="3">
+      <c r="Q3" s="3">
         <v>1.0</v>
       </c>
-      <c r="P3" s="3">
+      <c r="R3" s="3">
         <v>600.0</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="S3" s="3">
         <v>800000.0</v>
       </c>
-      <c r="R3" s="3">
+      <c r="T3" s="3">
         <v>0.1</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3362,11 +3405,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G4="","",IFERROR(VLOOKUP($G4,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I4" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G4="","",IFERROR(VLOOKUP($G4,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J4" s="3">
@@ -3378,29 +3421,31 @@
       <c r="L4" s="3">
         <v>4.0</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3">
         <v>0.0</v>
       </c>
-      <c r="N4" s="3">
+      <c r="P4" s="3">
         <v>0.0</v>
       </c>
-      <c r="O4" s="3">
+      <c r="Q4" s="3">
         <v>1.0</v>
       </c>
-      <c r="P4" s="3">
+      <c r="R4" s="3">
         <v>600.0</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="S4" s="3">
         <v>800000.0</v>
       </c>
-      <c r="R4" s="3">
+      <c r="T4" s="3">
         <v>0.1</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AB4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3427,11 +3472,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G5="","",IFERROR(VLOOKUP($G5,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I5" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G5="","",IFERROR(VLOOKUP($G5,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J5" s="3">
@@ -3443,29 +3488,31 @@
       <c r="L5" s="3">
         <v>4.0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3">
         <v>0.0</v>
       </c>
-      <c r="N5" s="3">
+      <c r="P5" s="3">
         <v>0.0</v>
       </c>
-      <c r="O5" s="3">
+      <c r="Q5" s="3">
         <v>1.0</v>
       </c>
-      <c r="P5" s="3">
+      <c r="R5" s="3">
         <v>600.0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="S5" s="3">
         <v>800000.0</v>
       </c>
-      <c r="R5" s="3">
+      <c r="T5" s="3">
         <v>0.1</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AB5" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3492,11 +3539,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G6="","",IFERROR(VLOOKUP($G6,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I6" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G6="","",IFERROR(VLOOKUP($G6,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J6" s="3">
@@ -3508,26 +3555,28 @@
       <c r="L6" s="3">
         <v>4.0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3">
         <v>0.0</v>
       </c>
-      <c r="N6" s="3">
+      <c r="P6" s="3">
         <v>0.0</v>
       </c>
-      <c r="O6" s="3">
+      <c r="Q6" s="3">
         <v>1.0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="R6" s="3">
         <v>600.0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="S6" s="3">
         <v>800000.0</v>
       </c>
-      <c r="R6" s="3">
+      <c r="T6" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3554,11 +3603,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G7="","",IFERROR(VLOOKUP($G7,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I7" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G7="","",IFERROR(VLOOKUP($G7,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J7" s="3">
@@ -3570,26 +3619,28 @@
       <c r="L7" s="3">
         <v>4.0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3">
         <v>0.0</v>
       </c>
-      <c r="N7" s="3">
+      <c r="P7" s="3">
         <v>0.0</v>
       </c>
-      <c r="O7" s="3">
+      <c r="Q7" s="3">
         <v>1.0</v>
       </c>
-      <c r="P7" s="3">
+      <c r="R7" s="3">
         <v>600.0</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="S7" s="3">
         <v>800000.0</v>
       </c>
-      <c r="R7" s="3">
+      <c r="T7" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3616,11 +3667,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G8="","",IFERROR(VLOOKUP($G8,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I8" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G8="","",IFERROR(VLOOKUP($G8,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J8" s="3">
@@ -3632,35 +3683,37 @@
       <c r="L8" s="3">
         <v>4.0</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3">
         <v>0.0</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>0.0</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1.0</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>600.0</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>800000.0</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>0.1</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AB8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AC8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3671,11 +3724,11 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G9="","",IFERROR(VLOOKUP($G9,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I9" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G9="","",IFERROR(VLOOKUP($G9,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J9" s="3"/>
@@ -3687,17 +3740,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AC9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AD9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3708,11 +3763,11 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G10="","",IFERROR(VLOOKUP($G10,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I10" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G10="","",IFERROR(VLOOKUP($G10,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J10" s="3"/>
@@ -3724,17 +3779,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="AB10" t="s">
         <v>264</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AC10" t="s">
         <v>262</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AD10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3745,11 +3802,11 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G11="","",IFERROR(VLOOKUP($G11,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I11" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G11="","",IFERROR(VLOOKUP($G11,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J11" s="3"/>
@@ -3761,17 +3818,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="AB11" t="s">
         <v>265</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AC11" t="s">
         <v>262</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AD11" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3782,11 +3841,11 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G12="","",IFERROR(VLOOKUP($G12,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I12" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G12="","",IFERROR(VLOOKUP($G12,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J12" s="3"/>
@@ -3798,8 +3857,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3810,11 +3871,11 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G13="","",IFERROR(VLOOKUP($G13,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I13" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G13="","",IFERROR(VLOOKUP($G13,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J13" s="3"/>
@@ -3826,8 +3887,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3838,11 +3901,11 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G14="","",IFERROR(VLOOKUP($G14,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I14" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G14="","",IFERROR(VLOOKUP($G14,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J14" s="3"/>
@@ -3854,8 +3917,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3866,11 +3931,11 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G15="","",IFERROR(VLOOKUP($G15,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I15" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G15="","",IFERROR(VLOOKUP($G15,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J15" s="3"/>
@@ -3882,8 +3947,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3894,11 +3961,11 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G16="","",IFERROR(VLOOKUP($G16,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I16" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G16="","",IFERROR(VLOOKUP($G16,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J16" s="3"/>
@@ -3910,8 +3977,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3922,11 +3991,11 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G17="","",IFERROR(VLOOKUP($G17,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I17" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G17="","",IFERROR(VLOOKUP($G17,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J17" s="3"/>
@@ -3938,8 +4007,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3950,11 +4021,11 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G18="","",IFERROR(VLOOKUP($G18,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I18" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G18="","",IFERROR(VLOOKUP($G18,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J18" s="3"/>
@@ -3966,8 +4037,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3978,11 +4051,11 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G19="","",IFERROR(VLOOKUP($G19,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I19" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G19="","",IFERROR(VLOOKUP($G19,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J19" s="3"/>
@@ -3994,8 +4067,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -4006,11 +4081,11 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G20="","",IFERROR(VLOOKUP($G20,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I20" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G20="","",IFERROR(VLOOKUP($G20,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J20" s="3"/>
@@ -4022,8 +4097,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -4034,11 +4111,11 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G21="","",IFERROR(VLOOKUP($G21,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I21" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G21="","",IFERROR(VLOOKUP($G21,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J21" s="3"/>
@@ -4050,8 +4127,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -4062,11 +4141,11 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G22="","",IFERROR(VLOOKUP($G22,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I22" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($G22="","",IFERROR(VLOOKUP($G22,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J22" s="3"/>
@@ -4078,39 +4157,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9639,6 +9720,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -9655,20 +9750,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11035,19 +11116,7 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AK7:AL7"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="V7:W7"/>
     <mergeCell ref="P7:Q7"/>
@@ -11064,7 +11133,19 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/docs/tutorials/files/xslope_reinforced_slope.xlsx
+++ b/docs/tutorials/files/xslope_reinforced_slope.xlsx
@@ -3346,7 +3346,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -3419,7 +3419,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -3486,7 +3486,7 @@
         <v>4.0</v>
       </c>
       <c r="L5" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -3553,7 +3553,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -3617,7 +3617,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3681,7 +3681,7 @@
         <v>4.0</v>
       </c>
       <c r="L8" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>

--- a/docs/tutorials/files/xslope_reinforced_slope.xlsx
+++ b/docs/tutorials/files/xslope_reinforced_slope.xlsx
@@ -3346,7 +3346,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -3419,7 +3419,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -3486,7 +3486,7 @@
         <v>4.0</v>
       </c>
       <c r="L5" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -3553,7 +3553,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -3617,7 +3617,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3681,7 +3681,7 @@
         <v>4.0</v>
       </c>
       <c r="L8" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>

--- a/docs/tutorials/files/xslope_reinforced_slope.xlsx
+++ b/docs/tutorials/files/xslope_reinforced_slope.xlsx
@@ -6851,7 +6851,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>1000000.0</v>
       </c>
@@ -6975,7 +6977,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>1000000.0</v>
       </c>

--- a/docs/tutorials/files/xslope_reinforced_slope.xlsx
+++ b/docs/tutorials/files/xslope_reinforced_slope.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D385E8-F13F-8F45-A02D-F28142715816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523500CF-89B8-4644-B955-31C74218CF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -875,9 +875,6 @@
   </si>
   <si>
     <t>I</t>
-  </si>
-  <si>
-    <t>Fixity</t>
   </si>
   <si>
     <t>P</t>
@@ -1122,6 +1119,21 @@
   </si>
   <si>
     <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
   </si>
 </sst>
 </file>
@@ -2128,16 +2140,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2152,8 +2164,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13398500" y="190499"/>
-          <a:ext cx="3156858" cy="2349501"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2458,7 +2470,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2470,8 +2482,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2823,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3005,7 +3063,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>313</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -3017,7 +3075,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -3029,28 +3087,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3094,7 +3158,7 @@
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -3192,7 +3256,7 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -3210,10 +3274,10 @@
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3272,10 +3336,10 @@
         <v>252</v>
       </c>
       <c r="M2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="N2" s="27" t="s">
         <v>312</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>313</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>253</v>
@@ -3336,7 +3400,7 @@
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3">
@@ -3409,7 +3473,7 @@
         <v/>
       </c>
       <c r="I4" s="3" t="str">
-        <f>IF($G4="","",IFERROR(VLOOKUP($G4,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J4" s="3">
@@ -3476,7 +3540,7 @@
         <v/>
       </c>
       <c r="I5" s="3" t="str">
-        <f>IF($G5="","",IFERROR(VLOOKUP($G5,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J5" s="3">
@@ -3543,7 +3607,7 @@
         <v/>
       </c>
       <c r="I6" s="3" t="str">
-        <f>IF($G6="","",IFERROR(VLOOKUP($G6,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J6" s="3">
@@ -3607,7 +3671,7 @@
         <v/>
       </c>
       <c r="I7" s="3" t="str">
-        <f>IF($G7="","",IFERROR(VLOOKUP($G7,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J7" s="3">
@@ -3671,7 +3735,7 @@
         <v/>
       </c>
       <c r="I8" s="3" t="str">
-        <f>IF($G8="","",IFERROR(VLOOKUP($G8,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J8" s="3">
@@ -3728,7 +3792,7 @@
         <v/>
       </c>
       <c r="I9" s="3" t="str">
-        <f>IF($G9="","",IFERROR(VLOOKUP($G9,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J9" s="3"/>
@@ -3767,7 +3831,7 @@
         <v/>
       </c>
       <c r="I10" s="3" t="str">
-        <f>IF($G10="","",IFERROR(VLOOKUP($G10,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J10" s="3"/>
@@ -3806,7 +3870,7 @@
         <v/>
       </c>
       <c r="I11" s="3" t="str">
-        <f>IF($G11="","",IFERROR(VLOOKUP($G11,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J11" s="3"/>
@@ -3845,7 +3909,7 @@
         <v/>
       </c>
       <c r="I12" s="3" t="str">
-        <f>IF($G12="","",IFERROR(VLOOKUP($G12,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J12" s="3"/>
@@ -3875,7 +3939,7 @@
         <v/>
       </c>
       <c r="I13" s="3" t="str">
-        <f>IF($G13="","",IFERROR(VLOOKUP($G13,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J13" s="3"/>
@@ -3905,7 +3969,7 @@
         <v/>
       </c>
       <c r="I14" s="3" t="str">
-        <f>IF($G14="","",IFERROR(VLOOKUP($G14,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J14" s="3"/>
@@ -3935,7 +3999,7 @@
         <v/>
       </c>
       <c r="I15" s="3" t="str">
-        <f>IF($G15="","",IFERROR(VLOOKUP($G15,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J15" s="3"/>
@@ -3965,7 +4029,7 @@
         <v/>
       </c>
       <c r="I16" s="3" t="str">
-        <f>IF($G16="","",IFERROR(VLOOKUP($G16,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J16" s="3"/>
@@ -3995,7 +4059,7 @@
         <v/>
       </c>
       <c r="I17" s="3" t="str">
-        <f>IF($G17="","",IFERROR(VLOOKUP($G17,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J17" s="3"/>
@@ -4025,7 +4089,7 @@
         <v/>
       </c>
       <c r="I18" s="3" t="str">
-        <f>IF($G18="","",IFERROR(VLOOKUP($G18,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J18" s="3"/>
@@ -4055,7 +4119,7 @@
         <v/>
       </c>
       <c r="I19" s="3" t="str">
-        <f>IF($G19="","",IFERROR(VLOOKUP($G19,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J19" s="3"/>
@@ -4085,7 +4149,7 @@
         <v/>
       </c>
       <c r="I20" s="3" t="str">
-        <f>IF($G20="","",IFERROR(VLOOKUP($G20,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J20" s="3"/>
@@ -4115,7 +4179,7 @@
         <v/>
       </c>
       <c r="I21" s="3" t="str">
-        <f>IF($G21="","",IFERROR(VLOOKUP($G21,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J21" s="3"/>
@@ -4145,7 +4209,7 @@
         <v/>
       </c>
       <c r="I22" s="3" t="str">
-        <f>IF($G22="","",IFERROR(VLOOKUP($G22,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J22" s="3"/>
@@ -4201,18 +4265,18 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>194</v>
       </c>
@@ -4259,16 +4323,19 @@
         <v>257</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y2" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z2" t="s">
         <v>222</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -4287,14 +4354,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Y3" t="s">
-        <v>226</v>
-      </c>
+      <c r="Q3" s="3"/>
       <c r="Z3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AA3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -4313,8 +4381,12 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -4333,8 +4405,12 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -4353,8 +4429,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -4373,8 +4450,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -4393,8 +4471,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -4413,8 +4492,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -4433,8 +4513,9 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -4453,8 +4534,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -4473,36 +4555,37 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R15" s="42"/>
-      <c r="S15" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R16" s="26"/>
-      <c r="S16" s="9" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
-      <c r="R17" s="29"/>
-      <c r="S17" s="9" t="s">
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="29"/>
+      <c r="T17" s="9" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Y$2:$Y$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4534,10 +4617,10 @@
         <v>167</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4760,27 +4843,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4788,27 +4871,27 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" s="33"/>
       <c r="H3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -4849,10 +4932,10 @@
         <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4869,10 +4952,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" t="s">
         <v>284</v>
-      </c>
-      <c r="U5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4889,7 +4972,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -5178,27 +5261,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -5206,27 +5289,27 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -5267,10 +5350,10 @@
         <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5287,10 +5370,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" t="s">
         <v>284</v>
-      </c>
-      <c r="U5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5589,22 +5672,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="D2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5615,7 +5698,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5637,7 +5720,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5659,7 +5742,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5671,7 +5754,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5683,7 +5766,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5703,7 +5786,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6698,7 +6781,7 @@
         <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>114</v>
@@ -6767,22 +6850,22 @@
         <v>134</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>135</v>
       </c>
       <c r="AD10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AE10" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="AE10" s="46" t="s">
+      <c r="AF10" s="47" t="s">
         <v>308</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>309</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>136</v>
@@ -9724,20 +9807,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -9754,6 +9823,20 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11121,6 +11204,19 @@
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="V7:W7"/>
     <mergeCell ref="P7:Q7"/>
@@ -11137,19 +11233,6 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AK7:AL7"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AE4:AF4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11902,7 +11985,7 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
@@ -12463,7 +12546,7 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>

--- a/docs/tutorials/files/xslope_reinforced_slope.xlsx
+++ b/docs/tutorials/files/xslope_reinforced_slope.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523500CF-89B8-4644-B955-31C74218CF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12967D2-A998-D342-B5ED-43CABE326A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4780" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="319">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>vg</t>
-  </si>
-  <si>
-    <t>van Genuchten model (a, n)</t>
   </si>
   <si>
     <t>pow</t>
@@ -1134,6 +1131,12 @@
   </si>
   <si>
     <t>Unrotated</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n, l)</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -2881,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3063,7 +3066,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -3158,7 +3161,7 @@
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -3300,73 +3303,73 @@
   <sheetData>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="S2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="S2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="T2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>257</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>258</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>259</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
@@ -3397,11 +3400,11 @@
       </c>
       <c r="H3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I3" s="3" t="str">
         <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J3" s="3">
         <v>800.0</v>
@@ -3433,13 +3436,13 @@
         <v>0.1</v>
       </c>
       <c r="AB3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC3" t="s">
         <v>261</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>262</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
@@ -3470,11 +3473,11 @@
       </c>
       <c r="H4" s="3" t="str">
         <f>IF($G4="","",IFERROR(VLOOKUP($G4,$AB$8:$AD$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J4" s="3">
         <v>800.0</v>
@@ -3506,7 +3509,7 @@
         <v>0.1</v>
       </c>
       <c r="AB4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -3537,11 +3540,11 @@
       </c>
       <c r="H5" s="3" t="str">
         <f>IF($G5="","",IFERROR(VLOOKUP($G5,$AB$8:$AD$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J5" s="3">
         <v>800.0</v>
@@ -3573,7 +3576,7 @@
         <v>0.1</v>
       </c>
       <c r="AB5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
@@ -3604,11 +3607,11 @@
       </c>
       <c r="H6" s="3" t="str">
         <f>IF($G6="","",IFERROR(VLOOKUP($G6,$AB$8:$AD$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I6" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J6" s="3">
         <v>800.0</v>
@@ -3668,11 +3671,11 @@
       </c>
       <c r="H7" s="3" t="str">
         <f>IF($G7="","",IFERROR(VLOOKUP($G7,$AB$8:$AD$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I7" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J7" s="3">
         <v>800.0</v>
@@ -3732,11 +3735,11 @@
       </c>
       <c r="H8" s="3" t="str">
         <f>IF($G8="","",IFERROR(VLOOKUP($G8,$AB$8:$AD$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I8" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J8" s="3">
         <v>800.0</v>
@@ -3768,13 +3771,13 @@
         <v>0.1</v>
       </c>
       <c r="AB8" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC8" t="s">
         <v>258</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>259</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
@@ -3807,13 +3810,13 @@
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="AB9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="s">
         <v>261</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>262</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
@@ -3846,13 +3849,13 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="AB10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AC10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AD10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
@@ -3885,13 +3888,13 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AC11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AD11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
@@ -4235,7 +4238,7 @@
       <c r="L24" s="9"/>
       <c r="V24" s="26"/>
       <c r="W24" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.2">
@@ -4243,7 +4246,7 @@
       <c r="L25" s="9"/>
       <c r="V25" s="29"/>
       <c r="W25" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4278,61 +4281,61 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>271</v>
-      </c>
       <c r="O2" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P2" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q2" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>315</v>
-      </c>
       <c r="Z2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AA2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -4356,10 +4359,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AA3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -4383,7 +4386,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="Z4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -4407,7 +4410,7 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="Z5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -4570,13 +4573,13 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="S16" s="26"/>
       <c r="T16" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
       <c r="S17" s="29"/>
       <c r="T17" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4605,22 +4608,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E2" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4843,27 +4846,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4871,71 +4874,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F3" s="33"/>
       <c r="H3" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4952,10 +4955,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U5" t="s">
         <v>283</v>
-      </c>
-      <c r="U5" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4972,7 +4975,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -5261,27 +5264,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -5289,71 +5292,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5370,10 +5373,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U5" t="s">
         <v>283</v>
-      </c>
-      <c r="U5" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5672,22 +5675,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="50" t="s">
         <v>292</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="D2" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>296</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5698,7 +5701,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5720,7 +5723,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5742,7 +5745,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5754,7 +5757,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5766,7 +5769,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5786,7 +5789,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6597,16 +6600,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AP52"/>
+  <dimension ref="A2:AQ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="41" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
@@ -6621,7 +6624,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
@@ -6642,7 +6645,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
@@ -6664,67 +6667,67 @@
         <v>93</v>
       </c>
       <c r="AK4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" t="s">
         <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -6750,7 +6753,7 @@
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
@@ -6758,7 +6761,7 @@
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
       <c r="AG9" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
@@ -6769,136 +6772,140 @@
       <c r="AN9" s="54"/>
       <c r="AO9" s="54"/>
       <c r="AP9" s="54"/>
-    </row>
-    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AQ9" s="54"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>309</v>
-      </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AE10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>308</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AQ10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AP10" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -7021,10 +7028,13 @@
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AO11" s="3"/>
+      <c r="AO11" s="3">
+        <v>0.5</v>
+      </c>
       <c r="AP11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ11" s="3"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -7147,10 +7157,13 @@
       <c r="AN12" s="19">
         <v>0.0</v>
       </c>
-      <c r="AO12" s="19"/>
+      <c r="AO12" s="19">
+        <v>0.5</v>
+      </c>
       <c r="AP12" s="19"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ12" s="19"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -7195,8 +7208,9 @@
       <c r="AN13" s="19"/>
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ13" s="19"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -7241,8 +7255,9 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -7287,8 +7302,9 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -7333,8 +7349,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -7379,8 +7396,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -7425,8 +7443,9 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -7471,8 +7490,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -7517,8 +7537,9 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -7563,8 +7584,9 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -7609,8 +7631,9 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -7655,8 +7678,9 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -7701,8 +7725,9 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -7747,8 +7772,9 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -7781,8 +7807,9 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -7806,7 +7833,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -7830,7 +7857,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -7854,7 +7881,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -7878,7 +7905,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7902,7 +7929,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8408,7 +8435,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AG9:AP9"/>
+    <mergeCell ref="AG9:AQ9"/>
     <mergeCell ref="AA9:AF9"/>
     <mergeCell ref="C9:Z9"/>
   </mergeCells>
@@ -8488,7 +8515,7 @@
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM11:AN52">
+  <conditionalFormatting sqref="AM11:AO52">
     <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
     </cfRule>
@@ -8536,16 +8563,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="3">
         <v>-10.0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -8562,161 +8589,161 @@
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8725,12 +8752,12 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>shell</v>
       </c>
       <c r="B6" s="57"/>
       <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>base</v>
       </c>
       <c r="E6" s="57"/>
       <c r="G6" s="56" t="str">
@@ -8809,172 +8836,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9807,6 +9834,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -9823,20 +9864,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9870,277 +9897,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="D5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="G5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="J5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="M5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="P5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="W5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -10149,12 +10176,12 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="58" t="str">
         <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>shell</v>
       </c>
       <c r="B7" s="57"/>
       <c r="D7" s="58" t="str">
         <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>base</v>
       </c>
       <c r="E7" s="57"/>
       <c r="G7" s="58" t="str">
@@ -10233,172 +10260,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -11203,6 +11230,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
@@ -11219,20 +11260,6 @@
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="V7:W7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11329,20 +11356,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11350,7 +11377,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11361,19 +11388,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11386,7 +11413,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11395,10 +11422,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" t="s">
         <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11535,31 +11562,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11587,10 +11614,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11615,10 +11642,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11633,10 +11660,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11663,7 +11690,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11678,7 +11705,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11694,7 +11721,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11710,7 +11737,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11726,7 +11753,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11742,31 +11769,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11775,7 +11802,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11816,16 +11843,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11836,10 +11863,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
         <v>222</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11847,10 +11874,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
         <v>224</v>
-      </c>
-      <c r="F4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11858,10 +11885,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11991,122 +12018,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12552,122 +12579,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
